--- a/data/trans_orig/P43-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P43-Edad-trans_orig.xlsx
@@ -673,12 +673,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>18380</t>
+          <t>18205</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>37967</t>
+          <t>37832</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -688,12 +688,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -708,12 +708,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>18380</t>
+          <t>18205</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>37967</t>
+          <t>37832</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -723,12 +723,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>8,14%</t>
         </is>
       </c>
     </row>
@@ -751,12 +751,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>426799</t>
+          <t>426934</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>446386</t>
+          <t>446561</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>91,83%</t>
+          <t>91,86%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,05%</t>
+          <t>96,08%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -786,12 +786,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>426799</t>
+          <t>426934</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>446386</t>
+          <t>446561</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,83%</t>
+          <t>91,86%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,05%</t>
+          <t>96,08%</t>
         </is>
       </c>
     </row>
@@ -911,12 +911,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>64680</t>
+          <t>66409</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>99125</t>
+          <t>102058</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -926,12 +926,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>10,63%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>15,87%</t>
+          <t>16,34%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -946,12 +946,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>64680</t>
+          <t>66409</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>99125</t>
+          <t>102058</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -961,12 +961,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>10,63%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>15,87%</t>
+          <t>16,34%</t>
         </is>
       </c>
     </row>
@@ -989,12 +989,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>525386</t>
+          <t>522453</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>559831</t>
+          <t>558102</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1004,12 +1004,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>84,13%</t>
+          <t>83,66%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>89,64%</t>
+          <t>89,37%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1024,12 +1024,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>525386</t>
+          <t>522453</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>559831</t>
+          <t>558102</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1039,12 +1039,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>84,13%</t>
+          <t>83,66%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>89,64%</t>
+          <t>89,37%</t>
         </is>
       </c>
     </row>
@@ -1149,12 +1149,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>208264</t>
+          <t>209760</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>258799</t>
+          <t>258919</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1164,12 +1164,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>30,24%</t>
+          <t>30,45%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>37,57%</t>
+          <t>37,59%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1184,12 +1184,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>208264</t>
+          <t>209760</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>258799</t>
+          <t>258919</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>30,24%</t>
+          <t>30,45%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>37,57%</t>
+          <t>37,59%</t>
         </is>
       </c>
     </row>
@@ -1227,12 +1227,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>429965</t>
+          <t>429845</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>480500</t>
+          <t>479004</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1242,12 +1242,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>62,43%</t>
+          <t>62,41%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>69,76%</t>
+          <t>69,55%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1262,12 +1262,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>429965</t>
+          <t>429845</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>480500</t>
+          <t>479004</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1277,12 +1277,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>62,43%</t>
+          <t>62,41%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>69,76%</t>
+          <t>69,55%</t>
         </is>
       </c>
     </row>
@@ -1387,12 +1387,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>294349</t>
+          <t>293328</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>339156</t>
+          <t>339302</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1402,12 +1402,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>57,39%</t>
+          <t>57,19%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>66,12%</t>
+          <t>66,15%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1422,12 +1422,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>294349</t>
+          <t>293328</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>339156</t>
+          <t>339302</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1437,12 +1437,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>57,39%</t>
+          <t>57,19%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>66,12%</t>
+          <t>66,15%</t>
         </is>
       </c>
     </row>
@@ -1465,12 +1465,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>173779</t>
+          <t>173633</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>218586</t>
+          <t>219607</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1480,12 +1480,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>33,88%</t>
+          <t>33,85%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>42,61%</t>
+          <t>42,81%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>173779</t>
+          <t>173633</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>218586</t>
+          <t>219607</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1515,12 +1515,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>33,88%</t>
+          <t>33,85%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>42,61%</t>
+          <t>42,81%</t>
         </is>
       </c>
     </row>
@@ -1625,12 +1625,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>285802</t>
+          <t>287235</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>320313</t>
+          <t>320077</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1640,12 +1640,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>71,25%</t>
+          <t>71,61%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>79,86%</t>
+          <t>79,8%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>285802</t>
+          <t>287235</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>320313</t>
+          <t>320077</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>71,25%</t>
+          <t>71,61%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>79,86%</t>
+          <t>79,8%</t>
         </is>
       </c>
     </row>
@@ -1703,12 +1703,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>80798</t>
+          <t>81034</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>115309</t>
+          <t>113876</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1718,12 +1718,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>20,14%</t>
+          <t>20,2%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>28,75%</t>
+          <t>28,39%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -1738,12 +1738,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>80798</t>
+          <t>81034</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>115309</t>
+          <t>113876</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -1753,12 +1753,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>20,14%</t>
+          <t>20,2%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>28,75%</t>
+          <t>28,39%</t>
         </is>
       </c>
     </row>
@@ -1863,12 +1863,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>198672</t>
+          <t>198652</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>230404</t>
+          <t>232308</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -1883,7 +1883,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>67,93%</t>
+          <t>68,49%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -1898,12 +1898,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>198672</t>
+          <t>198652</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>230404</t>
+          <t>232308</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -1918,7 +1918,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>67,93%</t>
+          <t>68,49%</t>
         </is>
       </c>
     </row>
@@ -1941,12 +1941,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>108784</t>
+          <t>106880</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>140516</t>
+          <t>140536</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>32,07%</t>
+          <t>31,51%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1976,12 +1976,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>108784</t>
+          <t>106880</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>140516</t>
+          <t>140536</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>32,07%</t>
+          <t>31,51%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>78953</t>
+          <t>78472</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>113346</t>
+          <t>113475</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>24,05%</t>
+          <t>23,91%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>34,53%</t>
+          <t>34,57%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>78953</t>
+          <t>78472</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>113346</t>
+          <t>113475</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>24,05%</t>
+          <t>23,91%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>34,53%</t>
+          <t>34,57%</t>
         </is>
       </c>
     </row>
@@ -2179,12 +2179,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>214874</t>
+          <t>214745</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>249267</t>
+          <t>249748</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2194,12 +2194,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>65,47%</t>
+          <t>65,43%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>75,95%</t>
+          <t>76,09%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2214,12 +2214,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>214874</t>
+          <t>214745</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>249267</t>
+          <t>249748</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>65,47%</t>
+          <t>65,43%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>75,95%</t>
+          <t>76,09%</t>
         </is>
       </c>
     </row>
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1217806</t>
+          <t>1214792</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1326804</t>
+          <t>1330182</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -2354,12 +2354,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>36,25%</t>
+          <t>36,16%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>39,49%</t>
+          <t>39,59%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -2374,12 +2374,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1217806</t>
+          <t>1214792</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1326804</t>
+          <t>1330182</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -2389,12 +2389,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>36,25%</t>
+          <t>36,16%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>39,49%</t>
+          <t>39,59%</t>
         </is>
       </c>
     </row>
@@ -2417,12 +2417,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2032690</t>
+          <t>2029312</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2141688</t>
+          <t>2144702</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -2432,12 +2432,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>60,51%</t>
+          <t>60,41%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>63,75%</t>
+          <t>63,84%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -2452,12 +2452,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2032690</t>
+          <t>2029312</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2141688</t>
+          <t>2144702</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -2467,12 +2467,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>60,51%</t>
+          <t>60,41%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>63,75%</t>
+          <t>63,84%</t>
         </is>
       </c>
     </row>
@@ -2751,12 +2751,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>17921</t>
+          <t>16977</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>39485</t>
+          <t>39274</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2766,12 +2766,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>9,17%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2786,12 +2786,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>17921</t>
+          <t>16977</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>39485</t>
+          <t>39274</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2801,12 +2801,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>9,17%</t>
         </is>
       </c>
     </row>
@@ -2829,12 +2829,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>388792</t>
+          <t>389003</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>410356</t>
+          <t>411300</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2844,12 +2844,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>90,78%</t>
+          <t>90,83%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,82%</t>
+          <t>96,04%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>388792</t>
+          <t>389003</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>410356</t>
+          <t>411300</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2879,12 +2879,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>90,78%</t>
+          <t>90,83%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,82%</t>
+          <t>96,04%</t>
         </is>
       </c>
     </row>
@@ -2989,12 +2989,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>62853</t>
+          <t>65738</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>96967</t>
+          <t>99004</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3004,12 +3004,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>10,85%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,01%</t>
+          <t>16,34%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3024,12 +3024,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>62853</t>
+          <t>65738</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>96967</t>
+          <t>99004</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>10,85%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>16,01%</t>
+          <t>16,34%</t>
         </is>
       </c>
     </row>
@@ -3067,12 +3067,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>508830</t>
+          <t>506793</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>542944</t>
+          <t>540059</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3082,12 +3082,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>83,99%</t>
+          <t>83,66%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>89,62%</t>
+          <t>89,15%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3102,12 +3102,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>508830</t>
+          <t>506793</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>542944</t>
+          <t>540059</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3117,12 +3117,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>83,99%</t>
+          <t>83,66%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>89,62%</t>
+          <t>89,15%</t>
         </is>
       </c>
     </row>
@@ -3227,12 +3227,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>209763</t>
+          <t>210141</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>261305</t>
+          <t>261429</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3242,12 +3242,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>29,68%</t>
+          <t>29,73%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>36,97%</t>
+          <t>36,99%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>209763</t>
+          <t>210141</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>261305</t>
+          <t>261429</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3277,12 +3277,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>29,68%</t>
+          <t>29,73%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>36,97%</t>
+          <t>36,99%</t>
         </is>
       </c>
     </row>
@@ -3305,12 +3305,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>445541</t>
+          <t>445417</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>497083</t>
+          <t>496705</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3320,12 +3320,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>63,03%</t>
+          <t>63,01%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>70,32%</t>
+          <t>70,27%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3340,12 +3340,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>445541</t>
+          <t>445417</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>497083</t>
+          <t>496705</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3355,12 +3355,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>63,03%</t>
+          <t>63,01%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>70,32%</t>
+          <t>70,27%</t>
         </is>
       </c>
     </row>
@@ -3465,12 +3465,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>384436</t>
+          <t>385637</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>433670</t>
+          <t>434968</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3480,12 +3480,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>62,49%</t>
+          <t>62,69%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>70,5%</t>
+          <t>70,71%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3500,12 +3500,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>384436</t>
+          <t>385637</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>433670</t>
+          <t>434968</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3515,12 +3515,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>62,49%</t>
+          <t>62,69%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>70,5%</t>
+          <t>70,71%</t>
         </is>
       </c>
     </row>
@@ -3543,12 +3543,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>181483</t>
+          <t>180185</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>230717</t>
+          <t>229516</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3558,12 +3558,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>29,5%</t>
+          <t>29,29%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>37,51%</t>
+          <t>37,31%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3578,12 +3578,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>181483</t>
+          <t>180185</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>230717</t>
+          <t>229516</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3593,12 +3593,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>29,5%</t>
+          <t>29,29%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>37,51%</t>
+          <t>37,31%</t>
         </is>
       </c>
     </row>
@@ -3703,12 +3703,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>393822</t>
+          <t>394657</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>419907</t>
+          <t>419215</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>88,34%</t>
+          <t>88,52%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>94,19%</t>
+          <t>94,03%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -3738,12 +3738,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>393822</t>
+          <t>394657</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>419907</t>
+          <t>419215</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -3753,12 +3753,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>88,34%</t>
+          <t>88,52%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>94,19%</t>
+          <t>94,03%</t>
         </is>
       </c>
     </row>
@@ -3781,12 +3781,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>25913</t>
+          <t>26605</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>51998</t>
+          <t>51163</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>11,48%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -3816,12 +3816,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>25913</t>
+          <t>26605</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>51998</t>
+          <t>51163</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -3831,12 +3831,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>11,48%</t>
         </is>
       </c>
     </row>
@@ -3941,12 +3941,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>285028</t>
+          <t>282980</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>313192</t>
+          <t>311888</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -3956,12 +3956,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>81,19%</t>
+          <t>80,61%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>89,21%</t>
+          <t>88,84%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -3976,12 +3976,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>285028</t>
+          <t>282980</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>313192</t>
+          <t>311888</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -3991,12 +3991,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>81,19%</t>
+          <t>80,61%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>89,21%</t>
+          <t>88,84%</t>
         </is>
       </c>
     </row>
@@ -4019,12 +4019,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>37865</t>
+          <t>39169</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>66029</t>
+          <t>68077</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -4034,12 +4034,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>18,81%</t>
+          <t>19,39%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -4054,12 +4054,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>37865</t>
+          <t>39169</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>66029</t>
+          <t>68077</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>18,81%</t>
+          <t>19,39%</t>
         </is>
       </c>
     </row>
@@ -4179,12 +4179,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>186522</t>
+          <t>185596</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>226943</t>
+          <t>226352</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -4194,12 +4194,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>48,62%</t>
+          <t>48,38%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>59,16%</t>
+          <t>59,01%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>186522</t>
+          <t>185596</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>226943</t>
+          <t>226352</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -4229,12 +4229,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>48,62%</t>
+          <t>48,38%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>59,16%</t>
+          <t>59,01%</t>
         </is>
       </c>
     </row>
@@ -4257,12 +4257,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>156665</t>
+          <t>157256</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>197086</t>
+          <t>198012</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -4272,12 +4272,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>40,84%</t>
+          <t>40,99%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>51,38%</t>
+          <t>51,62%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -4292,12 +4292,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>156665</t>
+          <t>157256</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>197086</t>
+          <t>198012</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -4307,12 +4307,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>40,84%</t>
+          <t>40,99%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>51,38%</t>
+          <t>51,62%</t>
         </is>
       </c>
     </row>
@@ -4417,12 +4417,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1607282</t>
+          <t>1611161</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1727835</t>
+          <t>1727789</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -4432,7 +4432,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>45,45%</t>
+          <t>45,56%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -4452,12 +4452,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1607282</t>
+          <t>1611161</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1727835</t>
+          <t>1727789</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -4467,7 +4467,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>45,45%</t>
+          <t>45,56%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -4495,12 +4495,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1808723</t>
+          <t>1808769</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1929276</t>
+          <t>1925397</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -4515,7 +4515,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>54,55%</t>
+          <t>54,44%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -4530,12 +4530,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1808723</t>
+          <t>1808769</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1929276</t>
+          <t>1925397</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -4550,7 +4550,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>54,55%</t>
+          <t>54,44%</t>
         </is>
       </c>
     </row>
@@ -4829,12 +4829,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>13836</t>
+          <t>14243</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>32066</t>
+          <t>30632</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4844,12 +4844,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4864,12 +4864,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>13836</t>
+          <t>14243</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>32066</t>
+          <t>30632</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4879,12 +4879,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>7,9%</t>
         </is>
       </c>
     </row>
@@ -4907,12 +4907,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>355600</t>
+          <t>357034</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>373830</t>
+          <t>373423</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4922,12 +4922,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>91,73%</t>
+          <t>92,1%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,43%</t>
+          <t>96,33%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4942,12 +4942,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>355600</t>
+          <t>357034</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>373830</t>
+          <t>373423</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4957,12 +4957,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,73%</t>
+          <t>92,1%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,43%</t>
+          <t>96,33%</t>
         </is>
       </c>
     </row>
@@ -5067,12 +5067,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>60676</t>
+          <t>60571</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>91820</t>
+          <t>90990</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5082,12 +5082,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,35%</t>
+          <t>16,2%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5102,12 +5102,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>60676</t>
+          <t>60571</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>91820</t>
+          <t>90990</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5117,12 +5117,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>16,35%</t>
+          <t>16,2%</t>
         </is>
       </c>
     </row>
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>469742</t>
+          <t>470572</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>500886</t>
+          <t>500991</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5160,12 +5160,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>83,65%</t>
+          <t>83,8%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>89,2%</t>
+          <t>89,21%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5180,12 +5180,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>469742</t>
+          <t>470572</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>500886</t>
+          <t>500991</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5195,12 +5195,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>83,65%</t>
+          <t>83,8%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>89,2%</t>
+          <t>89,21%</t>
         </is>
       </c>
     </row>
@@ -5305,12 +5305,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>201454</t>
+          <t>201511</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>251365</t>
+          <t>250641</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5320,12 +5320,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>30,62%</t>
+          <t>30,63%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>38,2%</t>
+          <t>38,09%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5340,12 +5340,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>201454</t>
+          <t>201511</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>251365</t>
+          <t>250641</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5355,12 +5355,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>30,62%</t>
+          <t>30,63%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>38,2%</t>
+          <t>38,09%</t>
         </is>
       </c>
     </row>
@@ -5383,12 +5383,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>406601</t>
+          <t>407325</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>456512</t>
+          <t>456455</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>61,8%</t>
+          <t>61,91%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>69,38%</t>
+          <t>69,37%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5418,12 +5418,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>406601</t>
+          <t>407325</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>456512</t>
+          <t>456455</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5433,12 +5433,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>61,8%</t>
+          <t>61,91%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>69,38%</t>
+          <t>69,37%</t>
         </is>
       </c>
     </row>
@@ -5543,12 +5543,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>401839</t>
+          <t>402216</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>448460</t>
+          <t>450180</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5558,12 +5558,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>62,1%</t>
+          <t>62,16%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>69,3%</t>
+          <t>69,57%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>401839</t>
+          <t>402216</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>448460</t>
+          <t>450180</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5593,12 +5593,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>62,1%</t>
+          <t>62,16%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>69,3%</t>
+          <t>69,57%</t>
         </is>
       </c>
     </row>
@@ -5621,12 +5621,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>198623</t>
+          <t>196903</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>245244</t>
+          <t>244867</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5636,12 +5636,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>30,7%</t>
+          <t>30,43%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>37,9%</t>
+          <t>37,84%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>198623</t>
+          <t>196903</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>245244</t>
+          <t>244867</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>30,7%</t>
+          <t>30,43%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>37,9%</t>
+          <t>37,84%</t>
         </is>
       </c>
     </row>
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>430164</t>
+          <t>431337</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>460956</t>
+          <t>459151</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5796,12 +5796,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>86,97%</t>
+          <t>87,21%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>93,2%</t>
+          <t>92,83%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5816,12 +5816,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>430164</t>
+          <t>431337</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>460956</t>
+          <t>459151</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5831,12 +5831,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>86,97%</t>
+          <t>87,21%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>93,2%</t>
+          <t>92,83%</t>
         </is>
       </c>
     </row>
@@ -5859,12 +5859,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>33658</t>
+          <t>35463</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>64450</t>
+          <t>63277</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5874,12 +5874,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>13,03%</t>
+          <t>12,79%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5894,12 +5894,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>33658</t>
+          <t>35463</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>64450</t>
+          <t>63277</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5909,12 +5909,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>13,03%</t>
+          <t>12,79%</t>
         </is>
       </c>
     </row>
@@ -6019,12 +6019,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>307069</t>
+          <t>308531</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>336383</t>
+          <t>335436</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>81,74%</t>
+          <t>82,12%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>89,54%</t>
+          <t>89,29%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6054,12 +6054,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>307069</t>
+          <t>308531</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>336383</t>
+          <t>335436</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>81,74%</t>
+          <t>82,12%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>89,54%</t>
+          <t>89,29%</t>
         </is>
       </c>
     </row>
@@ -6097,12 +6097,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>39304</t>
+          <t>40251</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>68618</t>
+          <t>67156</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>10,71%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>17,88%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6132,12 +6132,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>39304</t>
+          <t>40251</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>68618</t>
+          <t>67156</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>10,71%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>17,88%</t>
         </is>
       </c>
     </row>
@@ -6257,12 +6257,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>214220</t>
+          <t>214513</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>257258</t>
+          <t>259608</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6272,12 +6272,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>54,22%</t>
+          <t>54,29%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>65,11%</t>
+          <t>65,7%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6292,12 +6292,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>214220</t>
+          <t>214513</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>257258</t>
+          <t>259608</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6307,12 +6307,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>54,22%</t>
+          <t>54,29%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>65,11%</t>
+          <t>65,7%</t>
         </is>
       </c>
     </row>
@@ -6335,12 +6335,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>137854</t>
+          <t>135504</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>180892</t>
+          <t>180599</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6350,12 +6350,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>34,89%</t>
+          <t>34,3%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>45,78%</t>
+          <t>45,71%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6370,12 +6370,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>137854</t>
+          <t>135504</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>180892</t>
+          <t>180599</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6385,12 +6385,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>34,89%</t>
+          <t>34,3%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>45,78%</t>
+          <t>45,71%</t>
         </is>
       </c>
     </row>
@@ -6495,12 +6495,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1698387</t>
+          <t>1697844</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1824187</t>
+          <t>1820096</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6510,12 +6510,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>48,25%</t>
+          <t>48,24%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>51,83%</t>
+          <t>51,71%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6530,12 +6530,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1698387</t>
+          <t>1697844</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1824187</t>
+          <t>1820096</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6545,12 +6545,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>48,25%</t>
+          <t>48,24%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>51,83%</t>
+          <t>51,71%</t>
         </is>
       </c>
     </row>
@@ -6573,12 +6573,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1695503</t>
+          <t>1699594</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1821303</t>
+          <t>1821846</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6588,12 +6588,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>48,17%</t>
+          <t>48,29%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>51,75%</t>
+          <t>51,76%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6608,12 +6608,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1695503</t>
+          <t>1699594</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1821303</t>
+          <t>1821846</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6623,12 +6623,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>48,17%</t>
+          <t>48,29%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>51,75%</t>
+          <t>51,76%</t>
         </is>
       </c>
     </row>
@@ -6902,32 +6902,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>21297</t>
+          <t>21938</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10610</t>
+          <t>12527</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>37155</t>
+          <t>37831</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>12,51%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6937,32 +6937,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>21297</t>
+          <t>21938</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>10610</t>
+          <t>12527</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>37155</t>
+          <t>37831</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>12,51%</t>
         </is>
       </c>
     </row>
@@ -6980,32 +6980,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>242548</t>
+          <t>280364</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>226690</t>
+          <t>264471</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>253235</t>
+          <t>289775</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>91,93%</t>
+          <t>92,74%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>85,92%</t>
+          <t>87,49%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,98%</t>
+          <t>95,86%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7015,32 +7015,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>242548</t>
+          <t>280364</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>226690</t>
+          <t>264471</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>253235</t>
+          <t>289775</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>91,93%</t>
+          <t>92,74%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>85,92%</t>
+          <t>87,49%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,98%</t>
+          <t>95,86%</t>
         </is>
       </c>
     </row>
@@ -7058,17 +7058,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>263845</t>
+          <t>302302</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>263845</t>
+          <t>302302</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>263845</t>
+          <t>302302</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7093,17 +7093,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>263845</t>
+          <t>302302</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>263845</t>
+          <t>302302</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>263845</t>
+          <t>302302</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7140,32 +7140,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>51913</t>
+          <t>53580</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>26992</t>
+          <t>40715</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>70509</t>
+          <t>68964</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>14,51%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,84%</t>
+          <t>18,68%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7175,32 +7175,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>51913</t>
+          <t>53580</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>26992</t>
+          <t>40715</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>70509</t>
+          <t>68964</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>14,51%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>17,84%</t>
+          <t>18,68%</t>
         </is>
       </c>
     </row>
@@ -7218,32 +7218,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>343414</t>
+          <t>315641</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>324818</t>
+          <t>300257</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>368335</t>
+          <t>328506</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>86,87%</t>
+          <t>85,49%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>82,16%</t>
+          <t>81,32%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,17%</t>
+          <t>88,97%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7253,32 +7253,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>343414</t>
+          <t>315641</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>324818</t>
+          <t>300257</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>368335</t>
+          <t>328506</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>86,87%</t>
+          <t>85,49%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>82,16%</t>
+          <t>81,32%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,17%</t>
+          <t>88,97%</t>
         </is>
       </c>
     </row>
@@ -7296,17 +7296,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>395327</t>
+          <t>369221</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>395327</t>
+          <t>369221</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>395327</t>
+          <t>369221</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7331,17 +7331,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>395327</t>
+          <t>369221</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>395327</t>
+          <t>369221</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>395327</t>
+          <t>369221</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7378,32 +7378,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>126206</t>
+          <t>141599</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>111763</t>
+          <t>124901</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>140611</t>
+          <t>157486</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>33,98%</t>
+          <t>33,38%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>30,1%</t>
+          <t>29,44%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>37,86%</t>
+          <t>37,12%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7413,32 +7413,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>126206</t>
+          <t>141599</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>111763</t>
+          <t>124901</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>140611</t>
+          <t>157486</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>33,98%</t>
+          <t>33,38%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>30,1%</t>
+          <t>29,44%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>37,86%</t>
+          <t>37,12%</t>
         </is>
       </c>
     </row>
@@ -7456,32 +7456,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>245155</t>
+          <t>282634</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>230750</t>
+          <t>266747</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>259598</t>
+          <t>299332</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>66,02%</t>
+          <t>66,62%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>62,14%</t>
+          <t>62,88%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>69,9%</t>
+          <t>70,56%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7491,32 +7491,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>245155</t>
+          <t>282634</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>230750</t>
+          <t>266747</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>259598</t>
+          <t>299332</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>66,02%</t>
+          <t>66,62%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>62,14%</t>
+          <t>62,88%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>69,9%</t>
+          <t>70,56%</t>
         </is>
       </c>
     </row>
@@ -7534,17 +7534,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>371361</t>
+          <t>424233</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>371361</t>
+          <t>424233</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>371361</t>
+          <t>424233</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7569,17 +7569,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>371361</t>
+          <t>424233</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>371361</t>
+          <t>424233</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>371361</t>
+          <t>424233</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7616,32 +7616,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>326992</t>
+          <t>316513</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>303418</t>
+          <t>297700</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>363052</t>
+          <t>333761</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>64,63%</t>
+          <t>61,78%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>59,97%</t>
+          <t>58,1%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>71,76%</t>
+          <t>65,14%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7651,32 +7651,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>326992</t>
+          <t>316513</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>303418</t>
+          <t>297700</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>363052</t>
+          <t>333761</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>64,63%</t>
+          <t>61,78%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>59,97%</t>
+          <t>58,1%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>71,76%</t>
+          <t>65,14%</t>
         </is>
       </c>
     </row>
@@ -7694,32 +7694,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>178956</t>
+          <t>195838</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>142896</t>
+          <t>178590</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>202530</t>
+          <t>214651</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>35,37%</t>
+          <t>38,22%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>28,24%</t>
+          <t>34,86%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>40,03%</t>
+          <t>41,9%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7729,32 +7729,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>178956</t>
+          <t>195838</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>142896</t>
+          <t>178590</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>202530</t>
+          <t>214651</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>35,37%</t>
+          <t>38,22%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>28,24%</t>
+          <t>34,86%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>40,03%</t>
+          <t>41,9%</t>
         </is>
       </c>
     </row>
@@ -7772,17 +7772,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>505948</t>
+          <t>512351</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>505948</t>
+          <t>512351</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>505948</t>
+          <t>512351</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7807,17 +7807,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>505948</t>
+          <t>512351</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>505948</t>
+          <t>512351</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>505948</t>
+          <t>512351</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7854,32 +7854,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>322252</t>
+          <t>355760</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>309451</t>
+          <t>341704</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>333123</t>
+          <t>368182</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>80,33%</t>
+          <t>79,63%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>77,14%</t>
+          <t>76,49%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>83,04%</t>
+          <t>82,41%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7889,32 +7889,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>322252</t>
+          <t>355760</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>309451</t>
+          <t>341704</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>333123</t>
+          <t>368182</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>80,33%</t>
+          <t>79,63%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>77,14%</t>
+          <t>76,49%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>83,04%</t>
+          <t>82,41%</t>
         </is>
       </c>
     </row>
@@ -7932,32 +7932,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>78910</t>
+          <t>90987</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>68039</t>
+          <t>78565</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>91711</t>
+          <t>105043</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>19,67%</t>
+          <t>20,37%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>16,96%</t>
+          <t>17,59%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>22,86%</t>
+          <t>23,51%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7967,32 +7967,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>78910</t>
+          <t>90987</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>68039</t>
+          <t>78565</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>91711</t>
+          <t>105043</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>19,67%</t>
+          <t>20,37%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>16,96%</t>
+          <t>17,59%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>22,86%</t>
+          <t>23,51%</t>
         </is>
       </c>
     </row>
@@ -8010,17 +8010,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>401162</t>
+          <t>446747</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>401162</t>
+          <t>446747</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>401162</t>
+          <t>446747</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8045,17 +8045,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>401162</t>
+          <t>446747</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>401162</t>
+          <t>446747</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>401162</t>
+          <t>446747</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8092,32 +8092,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>476092</t>
+          <t>296622</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>440606</t>
+          <t>285904</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>510159</t>
+          <t>305785</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>90,47%</t>
+          <t>85,09%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>83,73%</t>
+          <t>82,02%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>96,94%</t>
+          <t>87,72%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8127,32 +8127,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>476092</t>
+          <t>296622</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>440606</t>
+          <t>285904</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>510159</t>
+          <t>305785</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>90,47%</t>
+          <t>85,09%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>83,73%</t>
+          <t>82,02%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>96,94%</t>
+          <t>87,72%</t>
         </is>
       </c>
     </row>
@@ -8170,32 +8170,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>50161</t>
+          <t>51968</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>16094</t>
+          <t>42805</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>85647</t>
+          <t>62686</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>14,91%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>12,28%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>17,98%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8205,32 +8205,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>50161</t>
+          <t>51968</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>16094</t>
+          <t>42805</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>85647</t>
+          <t>62686</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>14,91%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>12,28%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>17,98%</t>
         </is>
       </c>
     </row>
@@ -8248,17 +8248,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>526253</t>
+          <t>348590</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>526253</t>
+          <t>348590</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>526253</t>
+          <t>348590</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -8283,17 +8283,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>526253</t>
+          <t>348590</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>526253</t>
+          <t>348590</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>526253</t>
+          <t>348590</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -8330,32 +8330,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>258386</t>
+          <t>280479</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>245766</t>
+          <t>266020</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>270191</t>
+          <t>293725</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>70,39%</t>
+          <t>70,22%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>66,95%</t>
+          <t>66,6%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>73,61%</t>
+          <t>73,53%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8365,32 +8365,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>258386</t>
+          <t>280479</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>245766</t>
+          <t>266020</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>270191</t>
+          <t>293725</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>70,39%</t>
+          <t>70,22%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>66,95%</t>
+          <t>66,6%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>73,61%</t>
+          <t>73,53%</t>
         </is>
       </c>
     </row>
@@ -8408,32 +8408,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>108675</t>
+          <t>118963</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>96870</t>
+          <t>105717</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>121295</t>
+          <t>133422</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>29,61%</t>
+          <t>29,78%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>26,39%</t>
+          <t>26,47%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>33,05%</t>
+          <t>33,4%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8443,32 +8443,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>108675</t>
+          <t>118963</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>96870</t>
+          <t>105717</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>121295</t>
+          <t>133422</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>29,61%</t>
+          <t>29,78%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>26,39%</t>
+          <t>26,47%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>33,05%</t>
+          <t>33,4%</t>
         </is>
       </c>
     </row>
@@ -8486,17 +8486,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>367061</t>
+          <t>399442</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>367061</t>
+          <t>399442</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>367061</t>
+          <t>399442</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8521,17 +8521,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>367061</t>
+          <t>399442</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>367061</t>
+          <t>399442</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>367061</t>
+          <t>399442</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8568,32 +8568,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>1583137</t>
+          <t>1466492</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1445705</t>
+          <t>1418108</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1873457</t>
+          <t>1510341</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>55,92%</t>
+          <t>52,32%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>51,07%</t>
+          <t>50,59%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>66,18%</t>
+          <t>53,89%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -8603,32 +8603,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>1583137</t>
+          <t>1466492</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1445705</t>
+          <t>1418108</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1873457</t>
+          <t>1510341</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>55,92%</t>
+          <t>52,32%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>51,07%</t>
+          <t>50,59%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>66,18%</t>
+          <t>53,89%</t>
         </is>
       </c>
     </row>
@@ -8646,32 +8646,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>1247819</t>
+          <t>1336394</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>957499</t>
+          <t>1292545</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1385251</t>
+          <t>1384778</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>44,08%</t>
+          <t>47,68%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>33,82%</t>
+          <t>46,11%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>48,93%</t>
+          <t>49,41%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -8681,32 +8681,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>1247819</t>
+          <t>1336394</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>957499</t>
+          <t>1292545</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1385251</t>
+          <t>1384778</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>44,08%</t>
+          <t>47,68%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>33,82%</t>
+          <t>46,11%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>48,93%</t>
+          <t>49,41%</t>
         </is>
       </c>
     </row>
@@ -8724,17 +8724,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>2830956</t>
+          <t>2802886</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>2830956</t>
+          <t>2802886</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>2830956</t>
+          <t>2802886</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -8759,17 +8759,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>2830956</t>
+          <t>2802886</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>2830956</t>
+          <t>2802886</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>2830956</t>
+          <t>2802886</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
